--- a/Data Tugas Individu Analisis Regresi_Audryna Khairunnisa W_M0401241012.xlsx
+++ b/Data Tugas Individu Analisis Regresi_Audryna Khairunnisa W_M0401241012.xlsx
@@ -1,51 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\KULIAH\SEM 4\Anreg\Projek\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1F63817-2F36-47A7-98FE-AF3C227A6F84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="DATA" sheetId="1" r:id="rId5"/>
+    <sheet name="DATA" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="254">
-  <si>
-    <t>Data Kabupaten/Kota di Provinsi Jawa Tengah Tahun 2024</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="253">
   <si>
     <t>Kabupaten/Kota</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>X1</t>
-  </si>
-  <si>
-    <t>X2</t>
-  </si>
-  <si>
-    <t>X3</t>
-  </si>
-  <si>
-    <t>X4</t>
-  </si>
-  <si>
-    <t>X5</t>
-  </si>
-  <si>
-    <t>X6</t>
-  </si>
-  <si>
-    <t>X7</t>
-  </si>
-  <si>
-    <t>X8</t>
-  </si>
-  <si>
     <t>Kab. Banjarnegara</t>
   </si>
   <si>
@@ -773,42 +752,70 @@
   </si>
   <si>
     <t>X8 = Jumlah Rumah Sakit (Unit)</t>
+  </si>
+  <si>
+    <t>Angka Harapan Hidup</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rata-Rata Pengeluaran Per Kapita Sebulan (Juta Rupiah)</t>
+  </si>
+  <si>
+    <t>Rata-Rata Lama Sekolah (RLS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angka Harapan Lama Sekolah (HLS) </t>
+  </si>
+  <si>
+    <t>Tingkat Pengangguran Terbuka (TPT)</t>
+  </si>
+  <si>
+    <t>Tingkat Partisipasi Angkatan Kerja (TPAK)</t>
+  </si>
+  <si>
+    <t>Kepadatan Penduduk per Km Persegi (Km2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Jumlah Rumah Sakit (Unit)</t>
+  </si>
+  <si>
+    <t>Persentase Penduduk Miskin (Persen)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="6">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
       <b/>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
     </font>
@@ -818,11 +825,17 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -836,50 +849,45 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="11">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -887,7 +895,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -1077,1259 +1085,1274 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:J48"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="21.88"/>
-    <col customWidth="1" min="10" max="10" width="7.88"/>
+    <col min="1" max="1" width="21.88671875" customWidth="1"/>
+    <col min="2" max="2" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="56.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="31.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="37.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-    </row>
-    <row r="2">
+      <c r="B1" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>246</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>247</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="J1" s="9" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="10">
+        <v>993907</v>
+      </c>
+      <c r="E2" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="F2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="H2" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="I2" s="10">
+        <v>993</v>
+      </c>
+      <c r="J2" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
+      <c r="D3" s="10">
+        <v>1348026</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="G3" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="6">
-        <v>993907.0</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="H3" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="I3" s="10">
+        <v>1391</v>
+      </c>
+      <c r="J3" s="10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="B4" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="C4" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="6">
-        <v>993.0</v>
-      </c>
-      <c r="J3" s="6">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="D4" s="10">
+        <v>1246830</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="F4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="G4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="6">
-        <v>1348026.0</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="H4" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="I4" s="10">
+        <v>978</v>
+      </c>
+      <c r="J4" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="B5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="C5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="6">
-        <v>1391.0</v>
-      </c>
-      <c r="J4" s="6">
-        <v>18.0</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+      <c r="D5" s="10">
+        <v>1180266</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="F5" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D5" s="6">
-        <v>1246830.0</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="H5" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="I5" s="10">
+        <v>464</v>
+      </c>
+      <c r="J5" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="B6" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="C6" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="6">
-        <v>978.0</v>
-      </c>
-      <c r="J5" s="6">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
+      <c r="D6" s="10">
+        <v>1222659</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="F6" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="G6" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="D6" s="6">
-        <v>1180266.0</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="H6" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="I6" s="10">
+        <v>1017</v>
+      </c>
+      <c r="J6" s="10">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="B7" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="C7" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="I6" s="6">
-        <v>464.0</v>
-      </c>
-      <c r="J6" s="6">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
+      <c r="D7" s="10">
+        <v>1103010</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="F7" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="G7" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="D7" s="6">
-        <v>1222659.0</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="H7" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="I7" s="10">
+        <v>1167</v>
+      </c>
+      <c r="J7" s="10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="B8" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="C8" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="I7" s="6">
-        <v>1017.0</v>
-      </c>
-      <c r="J7" s="6">
-        <v>13.0</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
+      <c r="D8" s="10">
+        <v>1069596</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="F8" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="G8" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="6">
-        <v>1103010.0</v>
-      </c>
-      <c r="E8" s="6" t="s">
+      <c r="H8" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="I8" s="10">
+        <v>901</v>
+      </c>
+      <c r="J8" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="B9" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="C9" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="6">
-        <v>1167.0</v>
-      </c>
-      <c r="J8" s="6">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
+      <c r="D9" s="10">
+        <v>1210985</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="F9" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="G9" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="D9" s="6">
-        <v>1069596.0</v>
-      </c>
-      <c r="E9" s="6" t="s">
+      <c r="H9" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="I9" s="10">
+        <v>1396</v>
+      </c>
+      <c r="J9" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="B10" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="C10" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I9" s="6">
-        <v>901.0</v>
-      </c>
-      <c r="J9" s="6">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="10">
+        <v>1195114</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="F10" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="G10" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="6">
-        <v>1210985.0</v>
-      </c>
-      <c r="E10" s="6" t="s">
+      <c r="H10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="I10" s="10">
+        <v>762</v>
+      </c>
+      <c r="J10" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="B11" s="10" t="s">
         <v>65</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="C11" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="I10" s="6">
-        <v>1396.0</v>
-      </c>
-      <c r="J10" s="6">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
+      <c r="D11" s="10">
+        <v>1088544</v>
+      </c>
+      <c r="E11" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="F11" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="G11" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D11" s="6">
-        <v>1195114.0</v>
-      </c>
-      <c r="E11" s="6" t="s">
+      <c r="H11" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="I11" s="10">
+        <v>1228</v>
+      </c>
+      <c r="J11" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="B12" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="D12" s="10">
+        <v>1330909</v>
+      </c>
+      <c r="E12" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="I11" s="6">
-        <v>762.0</v>
-      </c>
-      <c r="J11" s="6">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
+      <c r="F12" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="G12" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="H12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I12" s="10">
+        <v>1253</v>
+      </c>
+      <c r="J12" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D12" s="6">
-        <v>1088544.0</v>
-      </c>
-      <c r="E12" s="6" t="s">
+      <c r="B13" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="C13" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="D13" s="10">
+        <v>1060534</v>
+      </c>
+      <c r="E13" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="6" t="s">
+      <c r="F13" s="10" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="6">
-        <v>1228.0</v>
-      </c>
-      <c r="J12" s="6">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
+      <c r="G13" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C13" s="6" t="s">
+      <c r="H13" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="D13" s="6">
-        <v>1330909.0</v>
-      </c>
-      <c r="E13" s="6" t="s">
+      <c r="I13" s="10">
+        <v>1060</v>
+      </c>
+      <c r="J13" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="B14" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="C14" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="H13" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="6">
-        <v>1253.0</v>
-      </c>
-      <c r="J13" s="6">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
+      <c r="D14" s="10">
+        <v>1266438</v>
+      </c>
+      <c r="E14" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="F14" s="10">
+        <v>13</v>
+      </c>
+      <c r="G14" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="H14" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="6">
-        <v>1060534.0</v>
-      </c>
-      <c r="E14" s="6" t="s">
+      <c r="I14" s="10">
+        <v>1062</v>
+      </c>
+      <c r="J14" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="B15" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="C15" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="D15" s="10">
+        <v>1472371</v>
+      </c>
+      <c r="E15" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I14" s="6">
-        <v>1060.0</v>
-      </c>
-      <c r="J14" s="6">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
+      <c r="F15" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="G15" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="H15" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D15" s="6">
-        <v>1266438.0</v>
-      </c>
-      <c r="E15" s="6" t="s">
+      <c r="I15" s="10">
+        <v>1846</v>
+      </c>
+      <c r="J15" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="6">
-        <v>13.0</v>
-      </c>
-      <c r="G15" s="6" t="s">
+      <c r="B16" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="H15" s="6" t="s">
+      <c r="C16" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="I15" s="6">
-        <v>1062.0</v>
-      </c>
-      <c r="J15" s="6">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
+      <c r="D16" s="10">
+        <v>1403301</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F16" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="G16" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="H16" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="D16" s="6">
-        <v>1472371.0</v>
-      </c>
-      <c r="E16" s="6" t="s">
+      <c r="I16" s="10">
+        <v>2077</v>
+      </c>
+      <c r="J16" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="B17" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="C17" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="D17" s="10">
+        <v>1048446</v>
+      </c>
+      <c r="E17" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="I16" s="6">
-        <v>1846.0</v>
-      </c>
-      <c r="J16" s="6">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
+      <c r="G17" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="H17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="I17" s="10">
+        <v>1236</v>
+      </c>
+      <c r="J17" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D17" s="6">
-        <v>1403301.0</v>
-      </c>
-      <c r="E17" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="F17" s="6" t="s">
+      <c r="B18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="D18" s="10">
+        <v>1333829</v>
+      </c>
+      <c r="E18" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="F18" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="I17" s="6">
-        <v>2077.0</v>
-      </c>
-      <c r="J17" s="6">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
+      <c r="G18" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="H18" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="I18" s="10">
+        <v>871</v>
+      </c>
+      <c r="J18" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D18" s="6">
-        <v>1048446.0</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="6" t="s">
+      <c r="B19" s="10">
+        <v>74</v>
+      </c>
+      <c r="C19" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="G18" s="6" t="s">
+      <c r="D19" s="10">
+        <v>1240752</v>
+      </c>
+      <c r="E19" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H18" s="6" t="s">
+      <c r="F19" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="I18" s="6">
-        <v>1236.0</v>
-      </c>
-      <c r="J18" s="6">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
+      <c r="G19" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="H19" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="6">
-        <v>1333829.0</v>
-      </c>
-      <c r="E19" s="6" t="s">
+      <c r="I19" s="10">
+        <v>1219</v>
+      </c>
+      <c r="J19" s="10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="B20" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="C20" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="D20" s="10">
+        <v>1188367</v>
+      </c>
+      <c r="E20" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="6">
-        <v>871.0</v>
-      </c>
-      <c r="J19" s="6">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
+      <c r="F20" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B20" s="6">
-        <v>74.0</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="G20" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="D20" s="6">
-        <v>1240752.0</v>
-      </c>
-      <c r="E20" s="6" t="s">
+      <c r="H20" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="I20" s="10">
+        <v>1382</v>
+      </c>
+      <c r="J20" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="6" t="s">
+      <c r="B21" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H20" s="6" t="s">
+      <c r="C21" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="I20" s="6">
-        <v>1219.0</v>
-      </c>
-      <c r="J20" s="6">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="5" t="s">
+      <c r="D21" s="10">
+        <v>1011402</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="F21" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="G21" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="6">
-        <v>1188367.0</v>
-      </c>
-      <c r="E21" s="6" t="s">
+      <c r="H21" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="I21" s="10">
+        <v>1334</v>
+      </c>
+      <c r="J21" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G21" s="6" t="s">
+      <c r="B22" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="H21" s="6" t="s">
+      <c r="C22" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="I21" s="6">
-        <v>1382.0</v>
-      </c>
-      <c r="J21" s="6">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="s">
+      <c r="D22" s="10">
+        <v>1094772</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="F22" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="G22" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="D22" s="6">
-        <v>1011402.0</v>
-      </c>
-      <c r="E22" s="6" t="s">
+      <c r="H22" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="I22" s="10">
+        <v>768</v>
+      </c>
+      <c r="J22" s="10">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A23" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="B23" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="C23" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="I22" s="6">
-        <v>1334.0</v>
-      </c>
-      <c r="J22" s="6">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="5" t="s">
+      <c r="D23" s="10">
+        <v>1262833</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="F23" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="G23" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="D23" s="6">
-        <v>1094772.0</v>
-      </c>
-      <c r="E23" s="6" t="s">
+      <c r="H23" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="I23" s="10">
+        <v>641</v>
+      </c>
+      <c r="J23" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="B24" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="C24" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="I23" s="6">
-        <v>768.0</v>
-      </c>
-      <c r="J23" s="6">
-        <v>11.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="s">
+      <c r="D24" s="10">
+        <v>1338257</v>
+      </c>
+      <c r="E24" s="10" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="F24" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="G24" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="D24" s="6">
-        <v>1262833.0</v>
-      </c>
-      <c r="E24" s="6" t="s">
+      <c r="H24" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="I24" s="10">
+        <v>1147</v>
+      </c>
+      <c r="J24" s="10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="C25" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I24" s="6">
-        <v>641.0</v>
-      </c>
-      <c r="J24" s="6">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="s">
+      <c r="D25" s="10">
+        <v>1251510</v>
+      </c>
+      <c r="E25" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="F25" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="G25" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="D25" s="6">
-        <v>1338257.0</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="H25" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="I25" s="10">
+        <v>1010</v>
+      </c>
+      <c r="J25" s="10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="B26" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="C26" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="I25" s="6">
-        <v>1147.0</v>
-      </c>
-      <c r="J25" s="6">
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="s">
+      <c r="D26" s="10">
+        <v>1473322</v>
+      </c>
+      <c r="E26" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="F26" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="G26" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="D26" s="6">
-        <v>1251510.0</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="H26" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="I26" s="10">
+        <v>2018</v>
+      </c>
+      <c r="J26" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="B27" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="C27" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="I26" s="6">
-        <v>1010.0</v>
-      </c>
-      <c r="J26" s="6">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="s">
+      <c r="D27" s="10">
+        <v>1062943</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F27" s="10" t="s">
         <v>172</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="G27" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="H27" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="D27" s="6">
-        <v>1473322.0</v>
-      </c>
-      <c r="E27" s="6" t="s">
+      <c r="I27" s="10">
+        <v>1702</v>
+      </c>
+      <c r="J27" s="10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="B28" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="C28" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="D28" s="10">
+        <v>1069204</v>
+      </c>
+      <c r="E28" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="G28" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="I27" s="6">
-        <v>2018.0</v>
-      </c>
-      <c r="J27" s="6">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="s">
+      <c r="H28" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="I28" s="10">
+        <v>936</v>
+      </c>
+      <c r="J28" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="B29" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="D28" s="6">
-        <v>1062943.0</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="F28" s="6" t="s">
+      <c r="C29" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="G28" s="6" t="s">
+      <c r="D29" s="10">
+        <v>1228377</v>
+      </c>
+      <c r="E29" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="H28" s="6" t="s">
+      <c r="F29" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="I28" s="6">
-        <v>1702.0</v>
-      </c>
-      <c r="J28" s="6">
-        <v>10.0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="5" t="s">
+      <c r="G29" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="H29" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="I29" s="10">
+        <v>588</v>
+      </c>
+      <c r="J29" s="10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="D29" s="6">
-        <v>1069204.0</v>
-      </c>
-      <c r="E29" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="G29" s="6" t="s">
+      <c r="B30" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="H29" s="6" t="s">
+      <c r="C30" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="I29" s="6">
-        <v>936.0</v>
-      </c>
-      <c r="J29" s="6">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="5" t="s">
+      <c r="D30" s="10">
+        <v>980047</v>
+      </c>
+      <c r="E30" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="F30" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="G30" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D30" s="6">
-        <v>1228377.0</v>
-      </c>
-      <c r="E30" s="6" t="s">
+      <c r="H30" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30" s="10">
+        <v>935</v>
+      </c>
+      <c r="J30" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="B31" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="C31" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="D31" s="10">
+        <v>1670272</v>
+      </c>
+      <c r="E31" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="F31" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="I30" s="6">
-        <v>588.0</v>
-      </c>
-      <c r="J30" s="6">
-        <v>9.0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="s">
+      <c r="G31" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="H31" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="I31" s="10">
+        <v>6600</v>
+      </c>
+      <c r="J31" s="10">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D31" s="6">
-        <v>980047.0</v>
-      </c>
-      <c r="E31" s="6" t="s">
+      <c r="B32" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="C32" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="D32" s="10">
+        <v>1485891</v>
+      </c>
+      <c r="E32" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="I31" s="6">
-        <v>935.0</v>
-      </c>
-      <c r="J31" s="6">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="s">
+      <c r="F32" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="G32" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="H32" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="D32" s="6">
-        <v>1670272.0</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="6" t="s">
+      <c r="I32" s="10">
+        <v>7096</v>
+      </c>
+      <c r="J32" s="10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="G32" s="6" t="s">
+      <c r="B33" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="H32" s="6" t="s">
+      <c r="C33" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="I32" s="6">
-        <v>6600.0</v>
-      </c>
-      <c r="J32" s="6">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="5" t="s">
+      <c r="D33" s="10">
+        <v>2126610</v>
+      </c>
+      <c r="E33" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="F33" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="G33" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="D33" s="6">
-        <v>1485891.0</v>
-      </c>
-      <c r="E33" s="6" t="s">
+      <c r="H33" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="I33" s="10">
+        <v>3661</v>
+      </c>
+      <c r="J33" s="10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="G33" s="6" t="s">
+      <c r="B34" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="H33" s="6" t="s">
+      <c r="C34" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="I33" s="6">
-        <v>7096.0</v>
-      </c>
-      <c r="J33" s="6">
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="s">
+      <c r="D34" s="10">
+        <v>2237774</v>
+      </c>
+      <c r="E34" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="F34" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="G34" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D34" s="6">
-        <v>2126610.0</v>
-      </c>
-      <c r="E34" s="6" t="s">
+      <c r="H34" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F34" s="6" t="s">
+      <c r="I34" s="10">
+        <v>4572</v>
+      </c>
+      <c r="J34" s="10">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G34" s="6" t="s">
+      <c r="B35" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="H34" s="6" t="s">
+      <c r="C35" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="I34" s="6">
-        <v>3661.0</v>
-      </c>
-      <c r="J34" s="6">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="5" t="s">
+      <c r="D35" s="10">
+        <v>1702139</v>
+      </c>
+      <c r="E35" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="F35" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="G35" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="D35" s="6">
-        <v>2237774.0</v>
-      </c>
-      <c r="E35" s="6" t="s">
+      <c r="H35" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="F35" s="6" t="s">
+      <c r="I35" s="10">
+        <v>11283</v>
+      </c>
+      <c r="J35" s="10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="G35" s="6" t="s">
+      <c r="B36" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="H35" s="6" t="s">
+      <c r="C36" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="I35" s="6">
-        <v>4572.0</v>
-      </c>
-      <c r="J35" s="6">
-        <v>25.0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="s">
+      <c r="D36" s="10">
+        <v>1489670</v>
+      </c>
+      <c r="E36" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="F36" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="G36" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="D36" s="6">
-        <v>1702139.0</v>
-      </c>
-      <c r="E36" s="6" t="s">
+      <c r="H36" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="I36" s="10">
+        <v>7200</v>
+      </c>
+      <c r="J36" s="10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="B39" s="4"/>
+      <c r="C39" s="4"/>
+      <c r="D39" s="4"/>
+    </row>
+    <row r="40" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="H36" s="6" t="s">
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="4"/>
+    </row>
+    <row r="41" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="I36" s="6">
-        <v>11283.0</v>
-      </c>
-      <c r="J36" s="6">
-        <v>16.0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="s">
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="4"/>
+    </row>
+    <row r="42" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+    </row>
+    <row r="43" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="B43" s="6"/>
+      <c r="C43" s="6"/>
+      <c r="D43" s="4"/>
+    </row>
+    <row r="44" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="D37" s="6">
-        <v>1489670.0</v>
-      </c>
-      <c r="E37" s="6" t="s">
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="4"/>
+    </row>
+    <row r="45" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="F37" s="6" t="s">
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="4"/>
+    </row>
+    <row r="46" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="G37" s="6" t="s">
+      <c r="B46" s="6"/>
+      <c r="C46" s="6"/>
+      <c r="D46" s="4"/>
+    </row>
+    <row r="47" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="H37" s="6" t="s">
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="4"/>
+    </row>
+    <row r="48" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="I37" s="6">
-        <v>7200.0</v>
-      </c>
-      <c r="J37" s="6">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="8" t="s">
-        <v>245</v>
-      </c>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D42" s="7"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="9" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="8" t="s">
-        <v>248</v>
-      </c>
-      <c r="D44" s="7"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="D45" s="7"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="8" t="s">
-        <v>250</v>
-      </c>
-      <c r="D46" s="7"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="D47" s="7"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="8" t="s">
-        <v>252</v>
-      </c>
-      <c r="D48" s="7"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="s">
-        <v>253</v>
-      </c>
-      <c r="D49" s="7"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A47:C47"/>
     <mergeCell ref="A48:C48"/>
-    <mergeCell ref="A49:C49"/>
+    <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A42:D42"/>
+    <mergeCell ref="A43:C43"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A45:C45"/>
     <mergeCell ref="A46:C46"/>
-    <mergeCell ref="A47:C47"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>